--- a/onboarding_forms/018_senior_care_onboarding_survey--onboarding_forms.xlsx
+++ b/onboarding_forms/018_senior_care_onboarding_survey--onboarding_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'primary_contact',_'label':_'primary',_'hint':_"the_individual's_primary_point_of_contact.",_'type':_'select_one',_'options':_[{'label':_'mother'},_{'label':_'brother'},_{'label':_'sister'},_{'label':_'son'},_{'label':_'daughter'},_{'label':_'wife'},_{'label':_'husband'},_{'label':_'other'}]}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'primary_contact', 'label': 'Primary', 'hint': "The individual's primary point of contact.", 'type': 'select_one', 'options': [{'label': 'Mother'}, {'label': 'Brother'}, {'label': 'Sister'}, {'label': 'Son'}, {'label': 'Daughter'}, {'label': 'Wife'}, {'label': 'Husband'}, {'label': 'Other'}]}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'secondary_contact',_'label':_'secondarycontact',_'type':_'text',_'options':_[]}</t>
+          <t>secondarycontact</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'secondary_contact', 'label': 'secondaryContact', 'type': 'text', 'options': []}</t>
+          <t>secondaryContact</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'address',_'label':_'address',_'type':_'select_multiple',_'options':_[{'label':_'street'},_{'label':_'suite'},_{'label':_'apt'},_{'label':_'city'},_{'label':_'state'},_{'label':_'zip'}]}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'address', 'label': 'address', 'type': 'select_multiple', 'options': [{'label': 'Street'}, {'label': 'Suite'}, {'label': 'Apt'}, {'label': 'City'}, {'label': 'State'}, {'label': 'Zip'}]}</t>
+          <t>address</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'emergency_contact_relationship',_'label':_'relationship',_'type':_'select_one',_'options':_[{'label':_'son'},_{'label':_'daughter'},_{'label':_'brother'},_{'label':_'sister'},_{'label':_'other'}]}</t>
+          <t>relationship</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'emergency_contact_relationship', 'label': 'relationship', 'type': 'select_one', 'options': [{'label': 'Son'}, {'label': 'Daughter'}, {'label': 'Brother'}, {'label': 'Sister'}, {'label': 'Other'}]}</t>
+          <t>relationship</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'emergency_contact_phone',_'label':_'phone',_'type':_'phone',_'options':_[]}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'emergency_contact_phone', 'label': 'phone', 'type': 'phone', 'options': []}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'emergency_contact_name',_'label':_'emergencycontactname',_'type':_'text',_'options':_[]}</t>
+          <t>emergencycontactname</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'emergency_contact_name', 'label': 'emergencyContactName', 'type': 'text', 'options': []}</t>
+          <t>emergencyContactName</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_"alzheimer's_disease"}</t>
+          <t>alzheimer's_disease</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': "Alzheimer's disease"}</t>
+          <t>Alzheimer's disease</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'arthritis'}</t>
+          <t>arthritis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Arthritis'}</t>
+          <t>Arthritis</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'heart_failure'}</t>
+          <t>heart_failure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Heart failure'}</t>
+          <t>Heart failure</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'stroke'}</t>
+          <t>stroke</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Stroke'}</t>
+          <t>Stroke</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'aspirin'}</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Aspirin'}</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'blood_thinner'}</t>
+          <t>blood_thinner</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Blood thinner'}</t>
+          <t>Blood thinner</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'knee_replacement_surgery'}</t>
+          <t>knee_replacement_surgery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Knee replacement surgery'}</t>
+          <t>Knee replacement surgery</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'hip_replacement_surgery'}</t>
+          <t>hip_replacement_surgery</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Hip replacement surgery'}</t>
+          <t>Hip replacement surgery</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
